--- a/assets/r04/sheets/空白玩家角色卡.xlsx
+++ b/assets/r04/sheets/空白玩家角色卡.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="空白玩家角色卡（主管）" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,18 +26,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="002B5797"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -49,16 +58,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002B5797"/>
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -67,74 +78,77 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
+      <left/>
       <right/>
-      <top/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top/>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,161 +511,1103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>空白玩家角色卡（主管）</t>
-        </is>
-      </c>
-    </row>
+          <t>凍結廢土 TRPG — 時間掠奪者角色卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>欄位</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>內容</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>基本資訊</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>角色名稱</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>角色姓名</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>掠奪者代號</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>玩家名稱</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>動機</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>年齡 / 舊世界身份</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>職位（主管/部長）</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>魅力 (Charm)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr"/>
-    </row>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>當前基地</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>外觀描述</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>智力 (Int)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr"/>
+          <t>五大屬性</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>體力 (Phys)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>值 (2–8)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>修正值 (ATT−5)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>咒力 (Curs)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>速度（SPD）</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="6">
+        <f>B10-5</f>
+        <v/>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>移動力、反應速度</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>心力 (Ment)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>知覺（PER）</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr"/>
+      <c r="C11" s="6">
+        <f>B11-5</f>
+        <v/>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>觀察力、預判、直覺</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>算力上限 (Sanli)</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>膽量（GUT）</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr"/>
+      <c r="C12" s="6">
+        <f>B12-5</f>
+        <v/>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>冷靜、意志力</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>滿意度 (ManYi)</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>技術（TEC）</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr"/>
+      <c r="C13" s="6">
+        <f>B13-5</f>
+        <v/>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>裝置操作、評估</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>資金 (Zijin)</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>經驗/備註</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
-    </row>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>交涉（NEG）</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="6">
+        <f>B14-5</f>
+        <v/>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>說服、談判</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>角色圖</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>【在此貼上角色圖片】</t>
-        </is>
-      </c>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>衍生屬性 (自動計算)</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="12" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="7" t="n"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>移動力（MV）</t>
+        </is>
+      </c>
+      <c r="B17" s="6">
+        <f>B10+3</f>
+        <v/>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>格/回合</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>速度值 + 3</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="7" t="n"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>前兆感知（FS）</t>
+        </is>
+      </c>
+      <c r="B18" s="6">
+        <f>B11-5</f>
+        <v/>
+      </c>
+      <c r="C18" s="9" t="inlineStr"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>知覺修正值</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="7" t="n"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>恐慌閾值（PT）</t>
+        </is>
+      </c>
+      <c r="B19" s="6">
+        <f>B12*2+5</f>
+        <v/>
+      </c>
+      <c r="C19" s="9" t="inlineStr"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>膽量值 × 2 + 5</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="7" t="n"/>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>時間抗性（TR）</t>
+        </is>
+      </c>
+      <c r="B20" s="6">
+        <f>B13-5</f>
+        <v/>
+      </c>
+      <c r="C20" s="9" t="inlineStr"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>技術修正值</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="8" t="n"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>生命值（HP） (最大)</t>
+        </is>
+      </c>
+      <c r="B21" s="6">
+        <f>B12*2+10</f>
+        <v/>
+      </c>
+      <c r="C21" s="9" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>膽量值 × 2 + 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>決心點 RP (最大)</t>
+        </is>
+      </c>
+      <c r="B22" s="6">
+        <f>MAX(B12-5,1)</f>
+        <v/>
+      </c>
+      <c r="C22" s="9" t="inlineStr"/>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>max(膽量修正值, 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>當前生命值（HP）</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>(手動填寫)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>當前決心點</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>(手動填寫)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>靈感點</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>/ 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>恐慌值</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>(起始=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>動機</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="12" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>動機類型</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>動機能力</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="12" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>凍結區經驗</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>經驗類型</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>經驗優勢</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>經驗直覺 (被動)</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>創傷</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="12" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>創傷類型</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>□ 未克服  □ 已克服 (轉為印記)</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>創傷效應 (劣勢情境)</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="12" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>決心效應 (優勢情境)</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="12" t="n"/>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>還在找的人</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="12" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr"/>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>關係</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr"/>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>最後已知位置</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="12" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>裝備</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="12" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>數值</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>重量</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>特殊效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>護甲</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr"/>
+      <c r="C48" s="6" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>武器 1</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr"/>
+      <c r="C49" s="6" t="inlineStr"/>
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>武器 2</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr"/>
+      <c r="C50" s="6" t="inlineStr"/>
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>探測器</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr"/>
+      <c r="C51" s="6" t="inlineStr"/>
+      <c r="D51" s="6" t="inlineStr"/>
+      <c r="E51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>工具 1</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr"/>
+      <c r="C52" s="6" t="inlineStr"/>
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>工具 2</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr"/>
+      <c r="C53" s="6" t="inlineStr"/>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>工具 3</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr"/>
+      <c r="C54" s="6" t="inlineStr"/>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>應急口糧 (天份)</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr"/>
+      <c r="C55" s="6" t="inlineStr"/>
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>急救包</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr"/>
+      <c r="C56" s="6" t="inlineStr"/>
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>解凍劑</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr"/>
+      <c r="C57" s="6" t="inlineStr"/>
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>信號彈</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr"/>
+      <c r="C58" s="6" t="inlineStr"/>
+      <c r="D58" s="6" t="inlineStr"/>
+      <c r="E58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>粉筆</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr"/>
+      <c r="C59" s="6" t="inlineStr"/>
+      <c r="D59" s="6" t="inlineStr"/>
+      <c r="E59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>淨水片</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr"/>
+      <c r="C60" s="6" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr"/>
+      <c r="C61" s="6" t="inlineStr"/>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>負重與資源</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n"/>
+      <c r="C63" s="11" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="11" t="n"/>
+      <c r="F63" s="12" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>當前負重</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr"/>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>/ 15 單位</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>攜帶時間結晶</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr"/>
+      <c r="C65" s="9">
+        <f>IF(B65="","",IF(B65&lt;=2,"無風險",IF(B65&lt;=5,"解凍骰+1",IF(B65&lt;=10,"解凍骰+2 + 技術DC10","解凍骰+3 + 知覺劣勢"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>廢鐵幣</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>儲存時間結晶</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>狀態追蹤</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n"/>
+      <c r="C69" s="11" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="11" t="n"/>
+      <c r="F69" s="12" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>寒冷疲勞等級</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr"/>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>0=正常 / 1=顫抖 / 2=遲鈍 / 3=失溫</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>凍結等級</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr"/>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>0=正常 / 1=凝滯 / 2=半凍 / 3=完全凍結</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>飢餓狀態</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr"/>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>正常 / 飢餓(24h) / 飢渴(48h) / 衰竭(72h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>上次進食 (回合/小時)</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>潛行修正</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr"/>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>重甲=劣勢 / 輕裝=優勢 / 恐慌=自動失敗</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>專長</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n"/>
+      <c r="C76" s="11" t="n"/>
+      <c r="D76" s="11" t="n"/>
+      <c r="E76" s="11" t="n"/>
+      <c r="F76" s="12" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>專長名稱</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>效果</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="n"/>
+      <c r="D77" s="12" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr"/>
+      <c r="B78" s="10" t="inlineStr"/>
+      <c r="C78" s="11" t="n"/>
+      <c r="D78" s="12" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr"/>
+      <c r="B79" s="10" t="inlineStr"/>
+      <c r="C79" s="11" t="n"/>
+      <c r="D79" s="12" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr"/>
+      <c r="B80" s="10" t="inlineStr"/>
+      <c r="C80" s="11" t="n"/>
+      <c r="D80" s="12" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr"/>
+      <c r="B81" s="10" t="inlineStr"/>
+      <c r="C81" s="11" t="n"/>
+      <c r="D81" s="12" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr"/>
+      <c r="B82" s="10" t="inlineStr"/>
+      <c r="C82" s="11" t="n"/>
+      <c r="D82" s="12" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr"/>
+      <c r="B83" s="10" t="inlineStr"/>
+      <c r="C83" s="11" t="n"/>
+      <c r="D83" s="12" t="n"/>
+    </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>成長記錄</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="n"/>
+      <c r="C85" s="11" t="n"/>
+      <c r="D85" s="11" t="n"/>
+      <c r="E85" s="11" t="n"/>
+      <c r="F85" s="12" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>里程碑</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>獲得獎勵</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>日期/遊戲次數</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr"/>
+      <c r="B87" s="6" t="inlineStr"/>
+      <c r="C87" s="6" t="inlineStr"/>
+      <c r="D87" s="6" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr"/>
+      <c r="B88" s="6" t="inlineStr"/>
+      <c r="C88" s="6" t="inlineStr"/>
+      <c r="D88" s="6" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr"/>
+      <c r="B89" s="6" t="inlineStr"/>
+      <c r="C89" s="6" t="inlineStr"/>
+      <c r="D89" s="6" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr"/>
+      <c r="B90" s="6" t="inlineStr"/>
+      <c r="C90" s="6" t="inlineStr"/>
+      <c r="D90" s="6" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr"/>
+      <c r="B91" s="6" t="inlineStr"/>
+      <c r="C91" s="6" t="inlineStr"/>
+      <c r="D91" s="6" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr"/>
+      <c r="B92" s="6" t="inlineStr"/>
+      <c r="C92" s="6" t="inlineStr"/>
+      <c r="D92" s="6" t="inlineStr"/>
+    </row>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>筆記 / 線索</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="n"/>
+      <c r="C94" s="11" t="n"/>
+      <c r="D94" s="11" t="n"/>
+      <c r="E94" s="11" t="n"/>
+      <c r="F94" s="12" t="n"/>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="8" t="inlineStr"/>
+      <c r="B95" s="11" t="n"/>
+      <c r="C95" s="11" t="n"/>
+      <c r="D95" s="11" t="n"/>
+      <c r="E95" s="11" t="n"/>
+      <c r="F95" s="12" t="n"/>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="8" t="inlineStr"/>
+      <c r="B96" s="11" t="n"/>
+      <c r="C96" s="11" t="n"/>
+      <c r="D96" s="11" t="n"/>
+      <c r="E96" s="11" t="n"/>
+      <c r="F96" s="12" t="n"/>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="8" t="inlineStr"/>
+      <c r="B97" s="11" t="n"/>
+      <c r="C97" s="11" t="n"/>
+      <c r="D97" s="11" t="n"/>
+      <c r="E97" s="11" t="n"/>
+      <c r="F97" s="12" t="n"/>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="8" t="inlineStr"/>
+      <c r="B98" s="11" t="n"/>
+      <c r="C98" s="11" t="n"/>
+      <c r="D98" s="11" t="n"/>
+      <c r="E98" s="11" t="n"/>
+      <c r="F98" s="12" t="n"/>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="8" t="inlineStr"/>
+      <c r="B99" s="11" t="n"/>
+      <c r="C99" s="11" t="n"/>
+      <c r="D99" s="11" t="n"/>
+      <c r="E99" s="11" t="n"/>
+      <c r="F99" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B16:B21"/>
+  <mergeCells count="34">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="B82:D82"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
